--- a/coretp/plans/svinval/SVINVAL_TP.xlsx
+++ b/coretp/plans/svinval/SVINVAL_TP.xlsx
@@ -5,10 +5,10 @@
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njoaquin/Documents/Clean Test Plans/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njoaquin/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA16AC50-5AA5-EC4C-AA33-E13F8735CF28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D3CA660-5BA7-5B4D-9236-50BB3AF27447}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="820" windowWidth="34560" windowHeight="20440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -252,12 +252,26 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -390,32 +404,38 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -708,13 +728,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="8"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="10"/>
     </row>
     <row r="2" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -746,7 +766,7 @@
       <c r="D3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="7" t="s">
         <v>34</v>
       </c>
     </row>
@@ -763,11 +783,11 @@
       <c r="D4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="11" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" ht="204" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -780,7 +800,7 @@
       <c r="D5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="6" t="s">
         <v>36</v>
       </c>
     </row>
@@ -797,7 +817,7 @@
       <c r="D6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="6" t="s">
         <v>37</v>
       </c>
     </row>
@@ -814,7 +834,7 @@
       <c r="D7" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="6" t="s">
         <v>38</v>
       </c>
     </row>
@@ -831,7 +851,7 @@
       <c r="D8" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="6" t="s">
         <v>39</v>
       </c>
     </row>
@@ -848,7 +868,7 @@
       <c r="D9" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="6" t="s">
         <v>40</v>
       </c>
     </row>
@@ -865,7 +885,7 @@
       <c r="D10" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="E10" s="6" t="s">
         <v>41</v>
       </c>
     </row>

--- a/coretp/plans/svinval/SVINVAL_TP.xlsx
+++ b/coretp/plans/svinval/SVINVAL_TP.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11130"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njoaquin/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njoaquin/Documents/Clean Test Plans/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D3CA660-5BA7-5B4D-9236-50BB3AF27447}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B82AEF59-1298-D349-AAE6-B39C14F80744}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="820" windowWidth="34560" windowHeight="20440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -186,17 +186,48 @@
 2. Execute SFENCE.INVAL.IR -&gt; expect ILLEGAL_INSTRUCTION</t>
   </si>
   <si>
+    <t>U-mode fault test:
+1. Allocate memory with VALID, READ, WRITE flags
+2. Execute SINVAL.VMA -&gt; expect ILLEGAL_INSTRUCTION</t>
+  </si>
+  <si>
+    <t>S-mode with TVM=1 fault test:
+1. Allocate memory with VALID, READ, WRITE flags
+2. Set mstatus.TVM=1 (bit 20)
+3. Execute SINVAL.VMA -&gt; expect ILLEGAL_INSTRUCTION</t>
+  </si>
+  <si>
+    <t>U-mode no-fault test for SFENCE ops:
+1. Set mstatus.TVM=1 (bit 20)
+2. Execute SFENCE.W.INVAL -&gt; expect ILLEGAL_INSTRUCTION
+3. Execute SFENCE.INVAL.IR -&gt; expect ILLEGAL_INSTRUCTION</t>
+  </si>
+  <si>
+    <t>Non-consecutive invalidation instructions:
+1. Load from memory (bring PTE into TLB)
+2. Store to memory -&gt; expect STORE_AMO_PAGE_FAULT (no W bit)
+3. Read leaf PTE and save for comparison
+4. Set W bit in PTE (OR with 0x4)
+5. Write modified PTE back
+6. Execute SFENCE.W.INVAL
+7. Execute random arithmetic operation
+8. Execute SINVAL.VMA
+9. Execute random arithmetic operation
+10. Execute SFENCE.INVAL.IR
+11. Store to memory (should succeed)
+12. Read leaf PTE and verify it changed</t>
+  </si>
+  <si>
     <t>1. Load from memory (bring PTE into TLB)
 2. Store to memory -&gt; expect STORE_AMO_PAGE_FAULT (no W bit)
 3. Read leaf PTE and save for comparison
 4. Set W bit in PTE (OR with 0x4)
 5. Write modified PTE back
-6. Store to memory -&gt; expect STORE_AMO_PAGE_FAULT (TLB has old PTE)
-7. Execute SFENCE.W.INVAL
-8. Execute SINVAL.VMA
-9. Execute SFENCE.INVAL.IR
-10. Store to memory (should succeed)
-11. Read leaf PTE and verify it changed</t>
+6. Execute SFENCE.W.INVAL
+7. Execute SINVAL.VMA
+8. Execute SFENCE.INVAL.IR
+9. Store to memory (should succeed)
+10. Read leaf PTE and verify it changed</t>
   </si>
   <si>
     <t>Multiple VAs (VA1, VA2, VA3):
@@ -205,66 +236,25 @@
 3. Read all leaf PTEs
 4. Set W bit in all PTEs
 5. Write all PTEs back
-6. Store to all -&gt; expect STORE_AMO_PAGE_FAULT (TLB has old PTEs)
-7. Execute SFENCE.W.INVAL
-8. Execute SINVAL.VMA for VA1
-9. Execute SINVAL.VMA for VA2
-10. Execute SINVAL.VMA for VA3
-11. Execute SFENCE.INVAL.IR
-12. Store to all (should succeed)
-13. Verify all PTEs changed</t>
-  </si>
-  <si>
-    <t>Non-consecutive invalidation instructions:
-1. Load from memory (bring PTE into TLB)
-2. Store to memory -&gt; expect STORE_AMO_PAGE_FAULT (no W bit)
-3. Read leaf PTE and save for comparison
-4. Set W bit in PTE (OR with 0x4)
-5. Write modified PTE back
-6. Store to memory -&gt; expect STORE_AMO_PAGE_FAULT (TLB has old PTE)
-7. Execute SFENCE.W.INVAL
-8. Execute random arithmetic operation
-9. Execute SINVAL.VMA
-10. Execute random arithmetic operation
-11. Execute SFENCE.INVAL.IR
-12. Store to memory (should succeed)
-13. Read leaf PTE and verify it changed</t>
-  </si>
-  <si>
-    <t>U-mode fault test:
-1. Allocate memory with VALID, READ, WRITE flags
-2. Execute SINVAL.VMA -&gt; expect ILLEGAL_INSTRUCTION</t>
-  </si>
-  <si>
-    <t>S-mode with TVM=1 fault test:
-1. Allocate memory with VALID, READ, WRITE flags
-2. Set mstatus.TVM=1 (bit 20)
-3. Execute SINVAL.VMA -&gt; expect ILLEGAL_INSTRUCTION</t>
-  </si>
-  <si>
-    <t>U-mode no-fault test for SFENCE ops:
-1. Set mstatus.TVM=1 (bit 20)
-2. Execute SFENCE.W.INVAL -&gt; expect ILLEGAL_INSTRUCTION
-3. Execute SFENCE.INVAL.IR -&gt; expect ILLEGAL_INSTRUCTION</t>
+6. Execute SFENCE.W.INVAL
+7. Execute SINVAL.VMA for VA1
+8. Execute SINVAL.VMA for VA2
+9. Execute SINVAL.VMA for VA3
+10. Execute SFENCE.INVAL.IR
+11. Store to all (should succeed)
+12. Verify all PTEs changed</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -404,38 +394,35 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -728,13 +715,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="10"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="9"/>
     </row>
     <row r="2" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -766,7 +753,7 @@
       <c r="D3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="10" t="s">
         <v>34</v>
       </c>
     </row>
@@ -783,11 +770,11 @@
       <c r="D4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="10" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="204" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" ht="170" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -800,11 +787,11 @@
       <c r="D5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="238" x14ac:dyDescent="0.2">
+      <c r="E5" s="10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="221" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -817,11 +804,11 @@
       <c r="D6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="255" x14ac:dyDescent="0.2">
+      <c r="E6" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="221" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -834,8 +821,8 @@
       <c r="D7" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="6" t="s">
-        <v>38</v>
+      <c r="E7" s="10" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="51" x14ac:dyDescent="0.2">
@@ -852,7 +839,7 @@
         <v>25</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="68" x14ac:dyDescent="0.2">
@@ -869,7 +856,7 @@
         <v>28</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="85" x14ac:dyDescent="0.2">
@@ -886,7 +873,7 @@
         <v>32</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
@@ -915,15 +902,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100815CC0311B58BB469E58C0B9C6D5A1E3" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a19fa265d978d88ed6a7b13c74bee12e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e8037ae1-f799-41f0-b119-cbea2f4ab5d4" xmlns:ns3="b3c44bb9-2631-4400-93cf-11acafc6ee3a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1ebcff41a4cd7c30a8fef993265f2974" ns2:_="" ns3:_="">
     <xsd:import namespace="e8037ae1-f799-41f0-b119-cbea2f4ab5d4"/>
@@ -1172,6 +1150,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1184,14 +1171,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24752675-B760-43F1-B45D-4E8639F58F02}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A37CA4E4-13E9-4C3A-886D-534DD1626EFD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1210,6 +1189,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24752675-B760-43F1-B45D-4E8639F58F02}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3B00C00-0ACA-41F1-AF8B-41145D6DFC1C}">
   <ds:schemaRefs>

--- a/coretp/plans/svinval/SVINVAL_TP.xlsx
+++ b/coretp/plans/svinval/SVINVAL_TP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njoaquin/Documents/Clean Test Plans/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njoaquin/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B82AEF59-1298-D349-AAE6-B39C14F80744}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB7981C5-F164-7F44-9F99-E2170C50807E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="820" windowWidth="34560" windowHeight="20440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34560" yWindow="-13720" windowWidth="51200" windowHeight="27200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="svinval-TP" sheetId="7" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="73">
   <si>
     <t>Scenario details</t>
   </si>
@@ -165,96 +165,277 @@
     <t>Pseudo Ops V2</t>
   </si>
   <si>
-    <t>S-mode:
-1. Execute SINVAL.VMA (basic)
+    <t>SID_SVINVAL_09</t>
+  </si>
+  <si>
+    <t>TVM + SFENCE/SINVAL flow</t>
+  </si>
+  <si>
+    <t>Test SFENCE.W.INVAL -&gt; SINVAL.VMA -&gt; SFENCE.INVAL.IR flow with mstatus.TVM=1.
+SINVAL.VMA should fault as ILLEGAL_INSTRUCTION in S-mode when TVM is set.
+SFENCE.W.INVAL and SFENCE.INVAL.IR should NOT fault.</t>
+  </si>
+  <si>
+    <t>priv_mode = {s-mode}
+paging_mode = {sv39, sv48, sv57}</t>
+  </si>
+  <si>
+    <t>SID_SVINVAL_10</t>
+  </si>
+  <si>
+    <t>bare metal flow</t>
+  </si>
+  <si>
+    <t>Test SFENCE.W.INVAL -&gt; SINVAL.VMA -&gt; SFENCE.INVAL.IR flow in Bare Metal mode.
+No exceptions expected.</t>
+  </si>
+  <si>
+    <t>priv_mode = {s-mode}
+paging_mode = {bare/disabled}</t>
+  </si>
+  <si>
+    <t>SID_SVINVAL_11</t>
+  </si>
+  <si>
+    <t>M-mode flow</t>
+  </si>
+  <si>
+    <t>Test SFENCE.W.INVAL -&gt; SINVAL.VMA -&gt; SFENCE.INVAL.IR flow in Machine mode.
+No exceptions expected in M-mode.</t>
+  </si>
+  <si>
+    <t>priv_mode = {m-mode}
+paging_mode = {default}</t>
+  </si>
+  <si>
+    <t>SID_SVINVAL_12</t>
+  </si>
+  <si>
+    <t>SINVAL.VMA rs1=x0, rs2=non-x0</t>
+  </si>
+  <si>
+    <t>SINVAL.VMA opcode coverage: rs1=x0, rs2=non-x0 (ASID-based invalidation).
+Wrapped in SFENCE.W.INVAL / SFENCE.INVAL.IR sequence.</t>
+  </si>
+  <si>
+    <t>ASID-based invalidation (env: SV39/SV48/SV57, S-mode):
+1. mem = Memory(4K, VALID|READ|WRITE)
+2. asid = LoadImmediate(0x1)
+3. Execute SFENCE.W.INVAL
+4. Execute SINVAL.VMA(x0, asid) -&gt; ASID-based invalidation
+5. Execute SFENCE.INVAL.IR</t>
+  </si>
+  <si>
+    <t>SID_SVINVAL_13</t>
+  </si>
+  <si>
+    <t>SINVAL.VMA rs1=non-x0, rs2=x0</t>
+  </si>
+  <si>
+    <t>SINVAL.VMA opcode coverage: rs1=non-x0, rs2=x0 (VA-based invalidation).
+Wrapped in SFENCE.W.INVAL / SFENCE.INVAL.IR sequence.</t>
+  </si>
+  <si>
+    <t>VA-based invalidation (env: SV39/SV48/SV57, S-mode):
+1. mem = Memory(4K, VALID|READ|WRITE)
 2. Execute SFENCE.W.INVAL
-3. Execute SFENCE.INVAL.IR
-4. Verify execution success
-U-mode:
-1. Execute SFENCE.W.INVAL -&gt; expect ILLEGAL_INSTRUCTION
-2. Execute SFENCE.INVAL.IR -&gt; expect ILLEGAL_INSTRUCTION
-3. Verify exceptions</t>
-  </si>
-  <si>
-    <t>Test across all privilege modes and paging modes:
-S-mode:
-1. Execute SINVAL.VMA with various paging modes (SV39, SV48, SV57)
+3. sinval_src = LoadImmediate(mem)
+4. Execute SINVAL.VMA(sinval_src, x0) -&gt; VA-based invalidation
+5. Execute SFENCE.INVAL.IR</t>
+  </si>
+  <si>
+    <t>SID_SVINVAL_14</t>
+  </si>
+  <si>
+    <t>SINVAL.VMA rs1=non-x0, rs2=non-x0</t>
+  </si>
+  <si>
+    <t>SINVAL.VMA opcode coverage: rs1=non-x0, rs2=non-x0 (VA+ASID-based invalidation).
+Wrapped in SFENCE.W.INVAL / SFENCE.INVAL.IR sequence.</t>
+  </si>
+  <si>
+    <t>SID_SVINVAL_15</t>
+  </si>
+  <si>
+    <t>SINVAL.VMA rs1=x0, rs2=x0</t>
+  </si>
+  <si>
+    <t>SINVAL.VMA opcode coverage: rs1=x0, rs2=x0 (global invalidation).
+Wrapped in SFENCE.W.INVAL / SFENCE.INVAL.IR sequence.</t>
+  </si>
+  <si>
+    <t>Global invalidation (env: SV39/SV48/SV57, S-mode):
+1. Execute SFENCE.W.INVAL
+2. Directive("sinval.vma x0, x0") -&gt; global invalidation
+3. Execute SFENCE.INVAL.IR</t>
+  </si>
+  <si>
+    <t>S-mode opcode coverage (env: SV39/SV48/SV57, S-mode):
+1. mem = Memory(4K, VALID|READ|WRITE, modify=True)
+2. sinval_vma_src1 = LoadImmediate(mem)
+3. Execute SINVAL.VMA(sinval_vma_src1, x0)
+4. Execute SFENCE.W.INVAL
+5. Execute SFENCE.INVAL.IR
+6. one = LoadImmediate(1)
+7. AssertEqual(one, one) -&gt; verify execution success</t>
+  </si>
+  <si>
+    <t>U-mode opcode coverage (env: U-mode):
+1. sfence_w_inval = SFENCE.W.INVAL
+2. AssertException(ILLEGAL_INSTRUCTION, [sfence_w_inval])
+3. sfence_inval_ir = SFENCE.INVAL.IR
+4. AssertException(ILLEGAL_INSTRUCTION, [sfence_inval_ir])
+5. one = LoadImmediate(1)
+6. AssertEqual(one, one) -&gt; verify execution success</t>
+  </si>
+  <si>
+    <t>Invalidation sequence-1 (env: SV39/SV48/SV57, S-mode):
+1. mem = Memory(4K, VALID|READ, exclude WRITE, modify=True)
+2. Load(mem) -&gt; bring PTE into TLB
+3. store_val = LoadImmediate(0xDEAD)
+4. Store(mem, store_val) -&gt; AssertException(STORE_AMO_PAGE_FAULT)
+5. ReadLeafPTE(mem) -&gt; pte_val
+6. hold = Arithmetic(mv, pte_val)
+7. w_mask = LoadImmediate(1&lt;&lt;2)
+8. pte_with_w = Arithmetic(or, pte_val, w_mask)
+9. WriteLeafPTE(mem, pte_with_w)
+10. Execute SFENCE.W.INVAL
+11. sinval_src = LoadImmediate(mem)
+12. Execute SINVAL.VMA(sinval_src, x0)
+13. Execute SFENCE.INVAL.IR
+14. Store(mem, store_val) -&gt; verify write succeeds
+15. ReadLeafPTE(mem) -&gt; pte_after
+16. mv_after = Arithmetic(mv, pte_after)
+17. AssertNotEqual(hold, mv_after)</t>
+  </si>
+  <si>
+    <t>Invalidation sequence-2 multiple VAs (env: SV39/SV48/SV57, S-mode):
+1. mem1 = Memory(4K, VALID|READ, exclude WRITE, modify=True, or_mask=0x1000)
+2. mem2 = Memory(4K, VALID|READ, exclude WRITE, modify=True, or_mask=0x2000)
+3. mem3 = Memory(4K, VALID|READ, exclude WRITE, modify=True, or_mask=0x4000)
+4. Load(mem1), Load(mem2), Load(mem3) -&gt; bring PTEs into TLB
+5. store_val = LoadImmediate(0xDEAD)
+6. Store(mem1, store_val) -&gt; AssertException(STORE_AMO_PAGE_FAULT)
+7. Store(mem2, store_val) -&gt; AssertException(STORE_AMO_PAGE_FAULT)
+8. Store(mem3, store_val) -&gt; AssertException(STORE_AMO_PAGE_FAULT)
+9. For each mem: ReadLeafPTE -&gt; hold, OR with (1&lt;&lt;2), WriteLeafPTE
+10. Execute SFENCE.W.INVAL
+11. For each mem: sinval_src = LoadImmediate(mem), SINVAL.VMA(sinval_src, x0)
+12. Execute SFENCE.INVAL.IR
+13. Store(mem1, store_val), Store(mem2, store_val), Store(mem3, store_val)
+14. For each mem: ReadLeafPTE -&gt; pte_after, mv_after = Arithmetic(mv, pte_after)
+15. AssertNotEqual(hold_1, mv_after_1)
+16. AssertNotEqual(hold_2, mv_after_2)
+17. AssertNotEqual(hold_3, mv_after_3)</t>
+  </si>
+  <si>
+    <t>Non-consecutive invalidation (env: SV39/SV48/SV57, S-mode):
+1. mem = Memory(4K, VALID|READ, exclude WRITE, modify=True)
+2. Load(mem) -&gt; bring PTE into TLB
+3. store_val = LoadImmediate(0xDEAD)
+4. Store(mem, store_val) -&gt; AssertException(STORE_AMO_PAGE_FAULT)
+5. ReadLeafPTE(mem) -&gt; pte_val
+6. hold = Arithmetic(mv, pte_val)
+7. w_mask = LoadImmediate(1&lt;&lt;2)
+8. pte_with_w = Arithmetic(or, pte_val, w_mask)
+9. WriteLeafPTE(mem, pte_with_w)
+10. Execute SFENCE.W.INVAL
+11. Arithmetic() -&gt; random op
+12. sinval_src = LoadImmediate(mem)
+13. Execute SINVAL.VMA(sinval_src, x0)
+14. Arithmetic() -&gt; random op
+15. Execute SFENCE.INVAL.IR
+16. Store(mem, store_val) -&gt; verify write succeeds
+17. ReadLeafPTE(mem) -&gt; pte_after
+18. mv_after = Arithmetic(mv, pte_after)
+19. AssertNotEqual(hold, mv_after)</t>
+  </si>
+  <si>
+    <t>U-mode fault test (env: U-mode):
+1. mem = Memory(4K, VALID|READ|WRITE, modify=True)
+2. sinval_src = LoadImmediate(mem)
+3. sinval_instr = SINVAL.VMA(sinval_src, x0)
+4. AssertException(ILLEGAL_INSTRUCTION, [sinval_instr])</t>
+  </si>
+  <si>
+    <t>S-mode with TVM=1 fault test (env: SV39/SV48/SV57, S-mode):
+1. CsrWrite(mstatus, set_mask=1&lt;&lt;20) -&gt; set TVM=1
+2. mem = Memory(4K, VALID|READ|WRITE, modify=True)
+3. sinval_src = LoadImmediate(mem)
+4. sinval_instr = SINVAL.VMA(sinval_src, x0)
+5. AssertException(ILLEGAL_INSTRUCTION, [sinval_instr])</t>
+  </si>
+  <si>
+    <t>U-mode SFENCE fault test (env: U-mode):
+1. sfence_w_inval = SFENCE.W.INVAL
+2. AssertException(ILLEGAL_INSTRUCTION, [sfence_w_inval])
+3. sfence_inval_ir = SFENCE.INVAL.IR
+4. AssertException(ILLEGAL_INSTRUCTION, [sfence_inval_ir])</t>
+  </si>
+  <si>
+    <t>TVM=1 SFENCE/SINVAL flow (env: SV39/SV48/SV57, S-mode):
+1. CsrWrite(mstatus, set_mask=1&lt;&lt;20) -&gt; set TVM=1
+2. Execute SFENCE.W.INVAL -&gt; should NOT fault
+3. mem = Memory(4K, VALID|READ|WRITE, modify=True)
+4. sinval_src = LoadImmediate(mem)
+5. sinval_instr = SINVAL.VMA(sinval_src, x0)
+6. AssertException(ILLEGAL_INSTRUCTION, [sinval_instr])
+7. Execute SFENCE.INVAL.IR -&gt; should NOT fault</t>
+  </si>
+  <si>
+    <t>Bare Metal flow (env: DISABLED, S-mode):
+1. mem = Memory(4K, VALID|READ|WRITE, modify=True)
 2. Execute SFENCE.W.INVAL
-3. Execute SFENCE.INVAL.IR
-U-mode:
-1. Execute SFENCE.W.INVAL -&gt; expect ILLEGAL_INSTRUCTION
-2. Execute SFENCE.INVAL.IR -&gt; expect ILLEGAL_INSTRUCTION</t>
-  </si>
-  <si>
-    <t>U-mode fault test:
-1. Allocate memory with VALID, READ, WRITE flags
-2. Execute SINVAL.VMA -&gt; expect ILLEGAL_INSTRUCTION</t>
-  </si>
-  <si>
-    <t>S-mode with TVM=1 fault test:
-1. Allocate memory with VALID, READ, WRITE flags
-2. Set mstatus.TVM=1 (bit 20)
-3. Execute SINVAL.VMA -&gt; expect ILLEGAL_INSTRUCTION</t>
-  </si>
-  <si>
-    <t>U-mode no-fault test for SFENCE ops:
-1. Set mstatus.TVM=1 (bit 20)
-2. Execute SFENCE.W.INVAL -&gt; expect ILLEGAL_INSTRUCTION
-3. Execute SFENCE.INVAL.IR -&gt; expect ILLEGAL_INSTRUCTION</t>
-  </si>
-  <si>
-    <t>Non-consecutive invalidation instructions:
-1. Load from memory (bring PTE into TLB)
-2. Store to memory -&gt; expect STORE_AMO_PAGE_FAULT (no W bit)
-3. Read leaf PTE and save for comparison
-4. Set W bit in PTE (OR with 0x4)
-5. Write modified PTE back
-6. Execute SFENCE.W.INVAL
-7. Execute random arithmetic operation
-8. Execute SINVAL.VMA
-9. Execute random arithmetic operation
-10. Execute SFENCE.INVAL.IR
-11. Store to memory (should succeed)
-12. Read leaf PTE and verify it changed</t>
-  </si>
-  <si>
-    <t>1. Load from memory (bring PTE into TLB)
-2. Store to memory -&gt; expect STORE_AMO_PAGE_FAULT (no W bit)
-3. Read leaf PTE and save for comparison
-4. Set W bit in PTE (OR with 0x4)
-5. Write modified PTE back
-6. Execute SFENCE.W.INVAL
-7. Execute SINVAL.VMA
-8. Execute SFENCE.INVAL.IR
-9. Store to memory (should succeed)
-10. Read leaf PTE and verify it changed</t>
-  </si>
-  <si>
-    <t>Multiple VAs (VA1, VA2, VA3):
-1. Load from mem1, mem2, mem3 (bring PTEs into TLB)
-2. Store to all -&gt; expect STORE_AMO_PAGE_FAULT (no W bits)
-3. Read all leaf PTEs
-4. Set W bit in all PTEs
-5. Write all PTEs back
-6. Execute SFENCE.W.INVAL
-7. Execute SINVAL.VMA for VA1
-8. Execute SINVAL.VMA for VA2
-9. Execute SINVAL.VMA for VA3
-10. Execute SFENCE.INVAL.IR
-11. Store to all (should succeed)
-12. Verify all PTEs changed</t>
+3. sinval_src = LoadImmediate(mem)
+4. Execute SINVAL.VMA(sinval_src, x0)
+5. Execute SFENCE.INVAL.IR
+6. one = LoadImmediate(1)
+7. AssertEqual(one, one) -&gt; verify execution success</t>
+  </si>
+  <si>
+    <t>M-mode flow (env: M-mode):
+1. mem = Memory(4K, VALID|READ|WRITE, modify=True)
+2. Execute SFENCE.W.INVAL
+3. sinval_src = LoadImmediate(mem)
+4. Execute SINVAL.VMA(sinval_src, x0)
+5. Execute SFENCE.INVAL.IR
+6. one = LoadImmediate(1)
+7. AssertEqual(one, one) -&gt; verify execution success</t>
+  </si>
+  <si>
+    <t>VA+ASID-based invalidation (env: SV39/SV48/SV57, S-mode):
+1. mem = Memory(4K, VALID|READ|WRITE)
+2. asid = LoadImmediate(0x1)
+3. Execute SFENCE.W.INVAL
+4. sinval_src = LoadImmediate(mem)
+5. Execute SINVAL.VMA(sinval_src, asid) -&gt; VA+ASID-based invalidation
+6. Execute SFENCE.INVAL.IR</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -394,40 +575,47 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -709,19 +897,19 @@
   <cols>
     <col min="1" max="1" width="21.5" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" customWidth="1"/>
-    <col min="3" max="3" width="54.1640625" customWidth="1"/>
-    <col min="4" max="4" width="29.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="61.6640625" customWidth="1"/>
+    <col min="3" max="3" width="113.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="47.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="124.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="11"/>
     </row>
     <row r="2" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -753,8 +941,8 @@
       <c r="D3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="10" t="s">
-        <v>34</v>
+      <c r="E3" s="7" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="170" x14ac:dyDescent="0.2">
@@ -770,11 +958,11 @@
       <c r="D4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="170" x14ac:dyDescent="0.2">
+      <c r="E4" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="306" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -787,11 +975,11 @@
       <c r="D5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="10" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="221" x14ac:dyDescent="0.2">
+      <c r="E5" s="6" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="306" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -804,11 +992,11 @@
       <c r="D6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="10" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="221" x14ac:dyDescent="0.2">
+      <c r="E6" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="340" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -821,11 +1009,11 @@
       <c r="D7" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+      <c r="E7" s="6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="85" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -838,11 +1026,11 @@
       <c r="D8" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="68" x14ac:dyDescent="0.2">
+      <c r="E8" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="102" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -855,8 +1043,8 @@
       <c r="D9" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E9" s="6" t="s">
-        <v>37</v>
+      <c r="E9" s="5" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="85" x14ac:dyDescent="0.2">
@@ -872,26 +1060,128 @@
       <c r="D10" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="136" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="136" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="4"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="4"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-    </row>
-    <row r="17" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C17" s="5"/>
+      <c r="B12" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="136" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="102" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="102" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15" t="s">
+        <v>52</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="119" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>54</v>
+      </c>
+      <c r="B16" t="s">
+        <v>55</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="68" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>57</v>
+      </c>
+      <c r="B17" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>60</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -902,6 +1192,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8037ae1-f799-41f0-b119-cbea2f4ab5d4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="b3c44bb9-2631-4400-93cf-11acafc6ee3a" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100815CC0311B58BB469E58C0B9C6D5A1E3" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a19fa265d978d88ed6a7b13c74bee12e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e8037ae1-f799-41f0-b119-cbea2f4ab5d4" xmlns:ns3="b3c44bb9-2631-4400-93cf-11acafc6ee3a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1ebcff41a4cd7c30a8fef993265f2974" ns2:_="" ns3:_="">
     <xsd:import namespace="e8037ae1-f799-41f0-b119-cbea2f4ab5d4"/>
@@ -1150,27 +1460,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24752675-B760-43F1-B45D-4E8639F58F02}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e8037ae1-f799-41f0-b119-cbea2f4ab5d4">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="b3c44bb9-2631-4400-93cf-11acafc6ee3a" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3B00C00-0ACA-41F1-AF8B-41145D6DFC1C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="e8037ae1-f799-41f0-b119-cbea2f4ab5d4"/>
+    <ds:schemaRef ds:uri="b3c44bb9-2631-4400-93cf-11acafc6ee3a"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A37CA4E4-13E9-4C3A-886D-534DD1626EFD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1187,23 +1496,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24752675-B760-43F1-B45D-4E8639F58F02}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3B00C00-0ACA-41F1-AF8B-41145D6DFC1C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="e8037ae1-f799-41f0-b119-cbea2f4ab5d4"/>
-    <ds:schemaRef ds:uri="b3c44bb9-2631-4400-93cf-11acafc6ee3a"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>